--- a/Employee_Reports_wi48/Lester John Fuentes Monter Q0607.xlsx
+++ b/Employee_Reports_wi48/Lester John Fuentes Monter Q0607.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1387,11 +1387,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1534,11 +1534,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1583,11 +1583,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1632,11 +1632,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1681,11 +1681,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1730,11 +1730,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1779,11 +1779,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1828,11 +1828,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1877,11 +1877,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1914,11 +1914,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1951,93 +1951,93 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>ASI- I  3.0 Profibus Gateway Configurations (SOPs)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>24-Aug-2025</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>ASI- I  3.0 Profibus Gateway Configurations (SOPs)</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Equipment Request &amp; Handover Procedure(AMH) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>24-Aug-2025</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>24-Aug-2026</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Equipment Request &amp; Handover Procedure(AMH) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>24-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -2062,11 +2062,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2099,11 +2099,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2136,11 +2136,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2173,11 +2173,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2210,11 +2210,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2247,11 +2247,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2296,11 +2296,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7655</v>
+        <v>7652</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7835</v>
+        <v>7832</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
